--- a/outputs/iteration-2/iteration-2-test-results.xlsx
+++ b/outputs/iteration-2/iteration-2-test-results.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rfcd182fb33594cba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test cases" sheetId="2" r:id="R77e2e14291514d02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="3" r:id="Rd608d4b0c08a4709"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R9c754a9c62df4eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test cases" sheetId="2" r:id="Rfb88e34a49974d7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings" sheetId="3" r:id="Rbf814687074549ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -510,7 +510,7 @@
         <x:v>Finding policy</x:v>
       </x:c>
       <x:c r="B28" s="3" t="str">
-        <x:v>7 confirmed open defects, 1 scope clarification (BUG-009), 1 observation (BUG-005).</x:v>
+        <x:v>7 confirmed open defects, 1 scope clarification (UC-004-SCOPE-001), 1 observation (OBS-001).</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="42" customHeight="1">
@@ -1151,7 +1151,7 @@
     </x:row>
     <x:row r="2" ht="70" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>BUG-001</x:v>
+        <x:v>UC-002-BUG-001</x:v>
       </x:c>
       <x:c r="B2" s="3" t="str">
         <x:v>Invoice PDF export fails</x:v>
@@ -1186,7 +1186,7 @@
     </x:row>
     <x:row r="3" ht="70" customHeight="1">
       <x:c r="A3" s="3" t="str">
-        <x:v>BUG-002</x:v>
+        <x:v>UC-003-BUG-001</x:v>
       </x:c>
       <x:c r="B3" s="3" t="str">
         <x:v>Checkout loses booking details and total</x:v>
@@ -1221,7 +1221,7 @@
     </x:row>
     <x:row r="4" ht="70" customHeight="1">
       <x:c r="A4" s="3" t="str">
-        <x:v>BUG-003</x:v>
+        <x:v>UC-003-BUG-002</x:v>
       </x:c>
       <x:c r="B4" s="3" t="str">
         <x:v>Dashboard displays sample booking</x:v>
@@ -1256,7 +1256,7 @@
     </x:row>
     <x:row r="5" ht="70" customHeight="1">
       <x:c r="A5" s="3" t="str">
-        <x:v>BUG-004</x:v>
+        <x:v>UC-002-BUG-002</x:v>
       </x:c>
       <x:c r="B5" s="3" t="str">
         <x:v>Malformed card values produce simulated success</x:v>
@@ -1291,7 +1291,7 @@
     </x:row>
     <x:row r="6" ht="70" customHeight="1">
       <x:c r="A6" s="3" t="str">
-        <x:v>BUG-005</x:v>
+        <x:v>OBS-001</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
         <x:v>Unused Supabase integration</x:v>
@@ -1326,7 +1326,7 @@
     </x:row>
     <x:row r="7" ht="70" customHeight="1">
       <x:c r="A7" s="3" t="str">
-        <x:v>BUG-006</x:v>
+        <x:v>UC-001-BUG-001</x:v>
       </x:c>
       <x:c r="B7" s="3" t="str">
         <x:v>Past tour date accepted</x:v>
@@ -1361,7 +1361,7 @@
     </x:row>
     <x:row r="8" ht="70" customHeight="1">
       <x:c r="A8" s="3" t="str">
-        <x:v>BUG-007</x:v>
+        <x:v>SETUP-BUG-001</x:v>
       </x:c>
       <x:c r="B8" s="3" t="str">
         <x:v>Clean Windows install fails</x:v>
@@ -1396,7 +1396,7 @@
     </x:row>
     <x:row r="9" ht="70" customHeight="1">
       <x:c r="A9" s="3" t="str">
-        <x:v>BUG-008</x:v>
+        <x:v>UC-004-BUG-001</x:v>
       </x:c>
       <x:c r="B9" s="3" t="str">
         <x:v>Quotation hydration runtime error</x:v>
@@ -1431,7 +1431,7 @@
     </x:row>
     <x:row r="10" ht="70" customHeight="1">
       <x:c r="A10" s="3" t="str">
-        <x:v>BUG-009</x:v>
+        <x:v>UC-004-SCOPE-001</x:v>
       </x:c>
       <x:c r="B10" s="3" t="str">
         <x:v>Quotation record submission is absent</x:v>
